--- a/gss_desc_stat_table.xlsx
+++ b/gss_desc_stat_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://1651wilkening-my.sharepoint.com/personal/canyon_white_convergint_com/Documents/Documents/GitHub/DATA 3010 Python Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_68DC4639B230921FD2FE31D2F8230B866055DDCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77E49AD4-BE1C-4D81-8230-8E200809E329}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_68DC4639B230921FD2FE31D2F8230B866055DDCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1A79C68-803C-4C2C-B91F-F1B0E93CB4D7}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>tvhours</t>
   </si>
@@ -72,14 +72,34 @@
   </si>
   <si>
     <t>mode</t>
+  </si>
+  <si>
+    <t>Quantitative Descriptive Statistics Table for GSS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -107,14 +127,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF66FF66"/>
+      <color rgb="FF33CC33"/>
+      <color rgb="FF99FF99"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -413,164 +445,180 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>397</v>
       </c>
-      <c r="C2">
+      <c r="C3">
         <v>397</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>397</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>3.0957178841309818</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>46.382871536523929</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>2.5113350125944578</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>45</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>25</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>0</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>19</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>22</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>89</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>31</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>4</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>60</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <f>(B9-B8)</f>
+      <c r="B11">
+        <f>(B10-B9)</f>
         <v>2</v>
       </c>
-      <c r="C10">
-        <f>(C9-C8)</f>
+      <c r="C11">
+        <f>(C10-C9)</f>
         <v>29</v>
       </c>
-      <c r="D10">
-        <f>(D9-D8)</f>
+      <c r="D11">
+        <f>(D10-D9)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>2.483461823197683</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>17.75420020915583</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>0.92550694877489625</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>